--- a/r4-JoanneumResearch-PreNUDGE-AppData-physical_activity/StructureDefinition-at-prenudge-observation-other-quantities.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-physical_activity/StructureDefinition-at-prenudge-observation-other-quantities.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-08T06:51:44+00:00</t>
+    <t>2026-06-25T12:51:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -87,7 +87,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This FHIR profile can be used for all the other Observations for PreNUDGE, beeing quantities and not fitting the existing narrow standardized observations. If some code for specifing a new Observation is missing, please contact prenudge@joanneum.at.</t>
+    <t>This FHIR profile can be used for all the other Observations for PreNUDGE, beeing quantities and not fitting the existing narrow standardized observations. If some code for specifying a new Observation is missing, please contact prenudge@joanneum.at.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -5865,7 +5865,7 @@
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="G32" t="s" s="2">
         <v>93</v>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-physical_activity/StructureDefinition-at-prenudge-observation-other-quantities.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-physical_activity/StructureDefinition-at-prenudge-observation-other-quantities.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-25T12:51:02+00:00</t>
+    <t>2026-06-29T13:58:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-physical_activity/StructureDefinition-at-prenudge-observation-other-quantities.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-physical_activity/StructureDefinition-at-prenudge-observation-other-quantities.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T13:58:40+00:00</t>
+    <t>2026-06-29T14:49:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-physical_activity/StructureDefinition-at-prenudge-observation-other-quantities.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-physical_activity/StructureDefinition-at-prenudge-observation-other-quantities.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T14:49:16+00:00</t>
+    <t>2026-06-29T16:38:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
